--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2024/2DO_TRIMESTRE/FRACCIONES XLII-XLVII/FRACC XLV/LTAIPT_A63F45A.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2024/2DO_TRIMESTRE/FRACCIONES XLII-XLVII/FRACC XLV/LTAIPT_A63F45A.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\COBAT\Downloads\SEGUNDO TRIMESTRE ABRIL-JUNIO 2024\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\COBAT\Downloads\TERCER TRIMESTRE JULIO-SEPTIEMBRE 2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAA380EB-0E66-42FB-B197-E5E1F01137DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73456F8D-985E-4E35-BA24-27F9EBA011EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="77">
   <si>
     <t>59952</t>
   </si>
@@ -129,34 +129,37 @@
     <t>Nota</t>
   </si>
   <si>
+    <t>4086F8C8D0FAAD66FB20C21DCAF8C2C1</t>
+  </si>
+  <si>
     <t>2024</t>
   </si>
   <si>
+    <t>01/07/2024</t>
+  </si>
+  <si>
+    <t>30/09/2024</t>
+  </si>
+  <si>
     <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202024/Depto.%20Transparencia/INVENTARIO%20DOCUMENTAL.xlsx</t>
   </si>
   <si>
     <t>15985257</t>
   </si>
   <si>
+    <t>Unidad de Transparencia</t>
+  </si>
+  <si>
+    <t>09/10/2024</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>A90CAB1C62F7C4F3A804C77CD8C54E3B</t>
-  </si>
-  <si>
-    <t>01/04/2024</t>
-  </si>
-  <si>
-    <t>30/06/2024</t>
-  </si>
-  <si>
     <t>14416246</t>
   </si>
   <si>
     <t>Unidad de Transparencia y Archivo</t>
-  </si>
-  <si>
-    <t>02/07/2024</t>
   </si>
   <si>
     <t>10184334</t>
@@ -819,34 +822,34 @@
     </row>
     <row r="8" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="H8" s="3" t="s">
+      <c r="J8" s="3" t="s">
         <v>41</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -860,7 +863,7 @@
     <mergeCell ref="G3:I3"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E8:E199" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E8:E193" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>Hidden_14</formula1>
     </dataValidation>
   </dataValidations>
@@ -920,124 +923,124 @@
     </row>
     <row r="2" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="C2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -1057,12 +1060,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
